--- a/results/tables/Table_S6_power_analysis.xlsx
+++ b/results/tables/Table_S6_power_analysis.xlsx
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>3.218640817777798</v>
+        <v>3.10754786707338</v>
       </c>
       <c r="D2" t="n">
-        <v>99.94196905032283</v>
+        <v>99.93458937629035</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -516,30 +516,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01909278525216073</v>
+        <v>1.020110360510401</v>
       </c>
       <c r="D3" t="n">
-        <v>65.94525350769145</v>
+        <v>99.67601749661173</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p &gt; 0.05</t>
+          <t>p &lt; 0.001</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.3623</v>
+        <v>0.9967</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9745</v>
+        <v>0.975</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.6219</v>
+        <v>0.6247</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9913</v>
+        <v>0.9926</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.8568</v>
+        <v>0.8556</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.977</v>
+        <v>0.9785</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.9971</v>
+        <v>0.9953</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.3085</v>
+        <v>0.3119</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.9483</v>
+        <v>0.95</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.22 x 10^0</t>
+          <t>3.11 x 10^0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1002,7 +1002,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -1012,36 +1012,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.91 x 10^-2</t>
+          <t>1.02 x 10^0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p &gt; 0.05</t>
+          <t>p &lt; 0.001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="G4" t="n">
